--- a/7. Brasil inputs/data EPE/Calculo da Demanda.xlsx
+++ b/7. Brasil inputs/data EPE/Calculo da Demanda.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SIN-model\7. Brasil inputs\data EPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF6DFB68-3DC5-428E-B55F-5E425EE11B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74704061-8152-4A8E-9D3B-C531A7CE8CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F804509D-198A-416F-8845-EE03261C4E2A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F804509D-198A-416F-8845-EE03261C4E2A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha3" sheetId="3" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="32" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="30">
   <si>
     <t>CARGA(P.U.DEMANDA MED.)</t>
   </si>
@@ -85,12 +89,60 @@
   <si>
     <t>Sistema 1</t>
   </si>
+  <si>
+    <t>sistema</t>
+  </si>
+  <si>
+    <t>ano</t>
+  </si>
+  <si>
+    <t>Southeast</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>Northeast</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>demanda</t>
+  </si>
+  <si>
+    <t>Soma de demanda</t>
+  </si>
+  <si>
+    <t>Rótulos de Coluna</t>
+  </si>
+  <si>
+    <t>Total Geral</t>
+  </si>
+  <si>
+    <t>Rótulos de Linha</t>
+  </si>
+  <si>
+    <t>MWh</t>
+  </si>
+  <si>
+    <t>MWm</t>
+  </si>
+  <si>
+    <t>GWh</t>
+  </si>
+  <si>
+    <t>GWm</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,6 +174,14 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -182,7 +242,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -199,21 +259,72 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 4" xfId="1" xr:uid="{6F28FF4B-9EF3-4029-AF61-93756C203C97}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="14">
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="35" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -224,6 +335,2163 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Calculo da Demanda.xlsx]Planilha3!Tabela dinâmica2</c:name>
+    <c:fmtId val="1"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha3!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>North</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha3!$A$5:$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2038</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha3!$B$5:$B$20</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>9.1326716860597763</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.5155144877937481</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.049965776865161</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10.302874743326489</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.603924252794888</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10.996577686516085</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11.413757700205338</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.723248916267396</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12.043919689710243</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12.480949121606207</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12.800365046771617</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13.139858544375999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13.509468400638832</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13.889915582934064</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14.272644307551905</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CD59-49EA-832D-23380CC4B966}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha3!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Northeast</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha3!$A$5:$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2038</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha3!$C$5:$C$20</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>21.982432124115903</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.727469769564223</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.70784850558978</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21.870978781656401</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22.066735112936346</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>22.434747889573348</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>22.684804928131417</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>22.995665069587044</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>23.33504449007529</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>23.700205338809038</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>24.103353867214238</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>24.528519279032626</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>25.014145562400184</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>25.555555555555557</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>26.134953228382386</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-CD59-49EA-832D-23380CC4B966}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha3!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>South</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha3!$A$5:$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2038</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha3!$D$5:$D$20</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>13.879534565366187</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.189025781428244</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.669404517453799</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15.204996577686515</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.82569016655259</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>16.472735569244808</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>17.125941136208077</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17.822381930184804</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18.533082363677845</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.300365046771617</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20.083390371891401</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.854209445585216</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21.688797627195985</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>22.546315309148984</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>23.364704540269219</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-CD59-49EA-832D-23380CC4B966}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha3!$E$3:$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Southeast</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha3!$A$5:$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2038</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha3!$E$5:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>50.312571298197582</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50.925507643166782</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>52.42961441934748</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>54.183093771389458</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>56.141341546885691</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>58.090691307323745</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60.084074834588186</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>62.253479352041978</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>64.476386036960989</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>66.846566278804474</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>69.293406342687661</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>71.818503308236373</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>74.431895961670094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>77.11419119324664</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>79.805612594113612</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-CD59-49EA-832D-23380CC4B966}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1737181216"/>
+        <c:axId val="1737176896"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1737181216"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1737176896"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1737176896"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1737181216"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>201930</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>12382</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>37147</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DA38C20-B2BD-D09E-2E2C-A6820EDED40A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Jonathan Veiga Velasco" refreshedDate="46177.716128703702" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{D7DB77C5-56BA-4B0F-A01F-33DF7A158226}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="U4:W64" sheet="Planilha1"/>
+  </cacheSource>
+  <cacheFields count="3">
+    <cacheField name="sistema" numFmtId="0">
+      <sharedItems count="4">
+        <s v="North"/>
+        <s v="Northeast"/>
+        <s v="South"/>
+        <s v="Southeast"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="ano" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2024" maxValue="2038" count="15">
+        <n v="2024"/>
+        <n v="2025"/>
+        <n v="2026"/>
+        <n v="2027"/>
+        <n v="2028"/>
+        <n v="2029"/>
+        <n v="2030"/>
+        <n v="2031"/>
+        <n v="2032"/>
+        <n v="2033"/>
+        <n v="2034"/>
+        <n v="2035"/>
+        <n v="2036"/>
+        <n v="2037"/>
+        <n v="2038"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="demanda" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="9.1326716860597763" maxValue="79.805612594113612"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="60">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="9.1326716860597763"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="9.5155144877937481"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="10.049965776865161"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="10.302874743326489"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="10.603924252794888"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="10.996577686516085"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="11.413757700205338"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <n v="11.723248916267396"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <n v="12.043919689710243"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <n v="12.480949121606207"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <n v="12.800365046771617"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <n v="13.139858544375999"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <n v="13.509468400638832"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <n v="13.889915582934064"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <n v="14.272644307551905"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="21.982432124115903"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="21.727469769564223"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="21.70784850558978"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="21.870978781656401"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="22.066735112936346"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="22.434747889573348"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <n v="22.684804928131417"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <n v="22.995665069587044"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <n v="23.33504449007529"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <n v="23.700205338809038"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <n v="24.103353867214238"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <n v="24.528519279032626"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <n v="25.014145562400184"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="13"/>
+    <n v="25.555555555555557"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="14"/>
+    <n v="26.134953228382386"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="13.879534565366187"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="14.189025781428244"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="14.669404517453799"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="15.204996577686515"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <n v="15.82569016655259"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <n v="16.472735569244808"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="6"/>
+    <n v="17.125941136208077"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="7"/>
+    <n v="17.822381930184804"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="8"/>
+    <n v="18.533082363677845"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <n v="19.300365046771617"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <n v="20.083390371891401"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="11"/>
+    <n v="20.854209445585216"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="12"/>
+    <n v="21.688797627195985"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="13"/>
+    <n v="22.546315309148984"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="14"/>
+    <n v="23.364704540269219"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="50.312571298197582"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="50.925507643166782"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="52.42961441934748"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="54.183093771389458"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="56.141341546885691"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="58.090691307323745"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="6"/>
+    <n v="60.084074834588186"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="7"/>
+    <n v="62.253479352041978"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="8"/>
+    <n v="64.476386036960989"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="9"/>
+    <n v="66.846566278804474"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="10"/>
+    <n v="69.293406342687661"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="11"/>
+    <n v="71.818503308236373"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="12"/>
+    <n v="74.431895961670094"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="13"/>
+    <n v="77.11419119324664"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="14"/>
+    <n v="79.805612594113612"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E50B019A-4514-4C6B-AF51-2E882850318C}" name="Tabela dinâmica2" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A3:F20" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="16">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Soma de demanda" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="5">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -542,585 +2810,2028 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2449C3-C936-4B91-B19C-2CEDCD2FFA02}">
+  <dimension ref="A3:F20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B5" s="14">
+        <v>9.1326716860597763</v>
+      </c>
+      <c r="C5" s="14">
+        <v>21.982432124115903</v>
+      </c>
+      <c r="D5" s="14">
+        <v>13.879534565366187</v>
+      </c>
+      <c r="E5" s="14">
+        <v>50.312571298197582</v>
+      </c>
+      <c r="F5" s="14">
+        <v>95.30720967373945</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="14">
+        <v>9.5155144877937481</v>
+      </c>
+      <c r="C6" s="14">
+        <v>21.727469769564223</v>
+      </c>
+      <c r="D6" s="14">
+        <v>14.189025781428244</v>
+      </c>
+      <c r="E6" s="14">
+        <v>50.925507643166782</v>
+      </c>
+      <c r="F6" s="14">
+        <v>96.357517681952999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="14">
+        <v>10.049965776865161</v>
+      </c>
+      <c r="C7" s="14">
+        <v>21.70784850558978</v>
+      </c>
+      <c r="D7" s="14">
+        <v>14.669404517453799</v>
+      </c>
+      <c r="E7" s="14">
+        <v>52.42961441934748</v>
+      </c>
+      <c r="F7" s="14">
+        <v>98.856833219256231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
+        <v>2027</v>
+      </c>
+      <c r="B8" s="14">
+        <v>10.302874743326489</v>
+      </c>
+      <c r="C8" s="14">
+        <v>21.870978781656401</v>
+      </c>
+      <c r="D8" s="14">
+        <v>15.204996577686515</v>
+      </c>
+      <c r="E8" s="14">
+        <v>54.183093771389458</v>
+      </c>
+      <c r="F8" s="14">
+        <v>101.56194387405887</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>2028</v>
+      </c>
+      <c r="B9" s="14">
+        <v>10.603924252794888</v>
+      </c>
+      <c r="C9" s="14">
+        <v>22.066735112936346</v>
+      </c>
+      <c r="D9" s="14">
+        <v>15.82569016655259</v>
+      </c>
+      <c r="E9" s="14">
+        <v>56.141341546885691</v>
+      </c>
+      <c r="F9" s="14">
+        <v>104.63769107916951</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>2029</v>
+      </c>
+      <c r="B10" s="14">
+        <v>10.996577686516085</v>
+      </c>
+      <c r="C10" s="14">
+        <v>22.434747889573348</v>
+      </c>
+      <c r="D10" s="14">
+        <v>16.472735569244808</v>
+      </c>
+      <c r="E10" s="14">
+        <v>58.090691307323745</v>
+      </c>
+      <c r="F10" s="14">
+        <v>107.99475245265799</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>2030</v>
+      </c>
+      <c r="B11" s="14">
+        <v>11.413757700205338</v>
+      </c>
+      <c r="C11" s="14">
+        <v>22.684804928131417</v>
+      </c>
+      <c r="D11" s="14">
+        <v>17.125941136208077</v>
+      </c>
+      <c r="E11" s="14">
+        <v>60.084074834588186</v>
+      </c>
+      <c r="F11" s="14">
+        <v>111.30857859913301</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
+        <v>2031</v>
+      </c>
+      <c r="B12" s="14">
+        <v>11.723248916267396</v>
+      </c>
+      <c r="C12" s="14">
+        <v>22.995665069587044</v>
+      </c>
+      <c r="D12" s="14">
+        <v>17.822381930184804</v>
+      </c>
+      <c r="E12" s="14">
+        <v>62.253479352041978</v>
+      </c>
+      <c r="F12" s="14">
+        <v>114.79477526808122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>2032</v>
+      </c>
+      <c r="B13" s="14">
+        <v>12.043919689710243</v>
+      </c>
+      <c r="C13" s="14">
+        <v>23.33504449007529</v>
+      </c>
+      <c r="D13" s="14">
+        <v>18.533082363677845</v>
+      </c>
+      <c r="E13" s="14">
+        <v>64.476386036960989</v>
+      </c>
+      <c r="F13" s="14">
+        <v>118.38843258042436</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>2033</v>
+      </c>
+      <c r="B14" s="14">
+        <v>12.480949121606207</v>
+      </c>
+      <c r="C14" s="14">
+        <v>23.700205338809038</v>
+      </c>
+      <c r="D14" s="14">
+        <v>19.300365046771617</v>
+      </c>
+      <c r="E14" s="14">
+        <v>66.846566278804474</v>
+      </c>
+      <c r="F14" s="14">
+        <v>122.32808578599133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>2034</v>
+      </c>
+      <c r="B15" s="14">
+        <v>12.800365046771617</v>
+      </c>
+      <c r="C15" s="14">
+        <v>24.103353867214238</v>
+      </c>
+      <c r="D15" s="14">
+        <v>20.083390371891401</v>
+      </c>
+      <c r="E15" s="14">
+        <v>69.293406342687661</v>
+      </c>
+      <c r="F15" s="14">
+        <v>126.28051562856491</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>2035</v>
+      </c>
+      <c r="B16" s="14">
+        <v>13.139858544375999</v>
+      </c>
+      <c r="C16" s="14">
+        <v>24.528519279032626</v>
+      </c>
+      <c r="D16" s="14">
+        <v>20.854209445585216</v>
+      </c>
+      <c r="E16" s="14">
+        <v>71.818503308236373</v>
+      </c>
+      <c r="F16" s="14">
+        <v>130.3410905772302</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
+        <v>2036</v>
+      </c>
+      <c r="B17" s="14">
+        <v>13.509468400638832</v>
+      </c>
+      <c r="C17" s="14">
+        <v>25.014145562400184</v>
+      </c>
+      <c r="D17" s="14">
+        <v>21.688797627195985</v>
+      </c>
+      <c r="E17" s="14">
+        <v>74.431895961670094</v>
+      </c>
+      <c r="F17" s="14">
+        <v>134.64430755190511</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
+        <v>2037</v>
+      </c>
+      <c r="B18" s="14">
+        <v>13.889915582934064</v>
+      </c>
+      <c r="C18" s="14">
+        <v>25.555555555555557</v>
+      </c>
+      <c r="D18" s="14">
+        <v>22.546315309148984</v>
+      </c>
+      <c r="E18" s="14">
+        <v>77.11419119324664</v>
+      </c>
+      <c r="F18" s="14">
+        <v>139.10597764088524</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="13">
+        <v>2038</v>
+      </c>
+      <c r="B19" s="14">
+        <v>14.272644307551905</v>
+      </c>
+      <c r="C19" s="14">
+        <v>26.134953228382386</v>
+      </c>
+      <c r="D19" s="14">
+        <v>23.364704540269219</v>
+      </c>
+      <c r="E19" s="14">
+        <v>79.805612594113612</v>
+      </c>
+      <c r="F19" s="14">
+        <v>143.57791467031711</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="11">
+        <v>175.87565594341774</v>
+      </c>
+      <c r="C20" s="11">
+        <v>349.8424595026238</v>
+      </c>
+      <c r="D20" s="11">
+        <v>271.56057494866525</v>
+      </c>
+      <c r="E20" s="11">
+        <v>948.20693588866084</v>
+      </c>
+      <c r="F20" s="11">
+        <v>1745.4856262833675</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D736287E-5306-43AF-9B42-BA3C78F3D6D1}">
-  <dimension ref="D1:Q18"/>
+  <dimension ref="D1:Y64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D1" s="6" t="s">
+    <row r="1" spans="4:25" x14ac:dyDescent="0.3">
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="F2" s="7" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="X1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="4:25" x14ac:dyDescent="0.3">
+      <c r="F2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D3" s="8" t="s">
+      <c r="X2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="4:25" x14ac:dyDescent="0.3">
+      <c r="D3" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D4" s="9">
+      <c r="X3" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="4:25" x14ac:dyDescent="0.3">
+      <c r="D4" s="8">
         <v>1</v>
       </c>
       <c r="E4">
         <v>2024</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <v>38284</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>38033</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <v>37791</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <v>33828</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <v>31633</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="9">
         <v>31015</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="9">
         <v>30757</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="9">
         <v>31499</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="9">
         <v>33600</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="9">
         <v>34313</v>
       </c>
-      <c r="P4" s="10">
+      <c r="P4" s="9">
         <v>34113</v>
       </c>
-      <c r="Q4" s="10">
+      <c r="Q4" s="9">
         <v>35352</v>
       </c>
-    </row>
-    <row r="7" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="U4" t="s">
+        <v>15</v>
+      </c>
+      <c r="V4" t="s">
+        <v>16</v>
+      </c>
+      <c r="W4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="4:25" x14ac:dyDescent="0.3">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" t="s">
+        <v>18</v>
+      </c>
+      <c r="V5">
+        <v>2024</v>
+      </c>
+      <c r="W5">
+        <f>X5/(730.5*12)</f>
+        <v>9.1326716860597763</v>
+      </c>
+      <c r="X5">
+        <v>80057</v>
+      </c>
+    </row>
+    <row r="6" spans="4:25" x14ac:dyDescent="0.3">
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6" t="s">
+        <v>18</v>
+      </c>
+      <c r="V6">
+        <v>2025</v>
+      </c>
+      <c r="W6">
+        <f t="shared" ref="W6:W64" si="0">X6/(730.5*12)</f>
+        <v>9.5155144877937481</v>
+      </c>
+      <c r="X6">
+        <v>83413</v>
+      </c>
+    </row>
+    <row r="7" spans="4:25" x14ac:dyDescent="0.3">
       <c r="E7" s="1">
         <v>45292</v>
       </c>
-    </row>
-    <row r="8" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="T7">
+        <v>2</v>
+      </c>
+      <c r="U7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V7">
+        <v>2026</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="0"/>
+        <v>10.049965776865161</v>
+      </c>
+      <c r="X7">
+        <v>88098</v>
+      </c>
+    </row>
+    <row r="8" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D8" s="2">
         <v>1</v>
       </c>
       <c r="E8" s="3">
         <v>1.37E-2</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <f>F$4*$E8</f>
         <v>524.49080000000004</v>
       </c>
-      <c r="G8" s="9">
-        <f t="shared" ref="G8:Q11" si="0">G$4*$E8</f>
+      <c r="G8" s="8">
+        <f t="shared" ref="G8:Q11" si="1">G$4*$E8</f>
         <v>521.0521</v>
       </c>
-      <c r="H8" s="9">
-        <f t="shared" si="0"/>
+      <c r="H8" s="8">
+        <f t="shared" si="1"/>
         <v>517.73670000000004</v>
       </c>
-      <c r="I8" s="9">
-        <f t="shared" si="0"/>
+      <c r="I8" s="8">
+        <f t="shared" si="1"/>
         <v>463.4436</v>
       </c>
-      <c r="J8" s="9">
-        <f t="shared" si="0"/>
+      <c r="J8" s="8">
+        <f t="shared" si="1"/>
         <v>433.37209999999999</v>
       </c>
-      <c r="K8" s="9">
-        <f t="shared" si="0"/>
+      <c r="K8" s="8">
+        <f t="shared" si="1"/>
         <v>424.90550000000002</v>
       </c>
-      <c r="L8" s="9">
-        <f t="shared" si="0"/>
+      <c r="L8" s="8">
+        <f t="shared" si="1"/>
         <v>421.37090000000001</v>
       </c>
-      <c r="M8" s="9">
-        <f t="shared" si="0"/>
+      <c r="M8" s="8">
+        <f t="shared" si="1"/>
         <v>431.53630000000004</v>
       </c>
-      <c r="N8" s="9">
-        <f t="shared" si="0"/>
+      <c r="N8" s="8">
+        <f t="shared" si="1"/>
         <v>460.32</v>
       </c>
-      <c r="O8" s="9">
-        <f t="shared" si="0"/>
+      <c r="O8" s="8">
+        <f t="shared" si="1"/>
         <v>470.0881</v>
       </c>
-      <c r="P8" s="9">
-        <f t="shared" si="0"/>
+      <c r="P8" s="8">
+        <f t="shared" si="1"/>
         <v>467.34809999999999</v>
       </c>
-      <c r="Q8" s="9">
-        <f t="shared" si="0"/>
+      <c r="Q8" s="8">
+        <f t="shared" si="1"/>
         <v>484.32240000000002</v>
       </c>
-    </row>
-    <row r="9" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="T8">
+        <v>3</v>
+      </c>
+      <c r="U8" t="s">
+        <v>18</v>
+      </c>
+      <c r="V8">
+        <v>2027</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="0"/>
+        <v>10.302874743326489</v>
+      </c>
+      <c r="X8">
+        <v>90315</v>
+      </c>
+    </row>
+    <row r="9" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D9" s="2">
         <v>2</v>
       </c>
       <c r="E9" s="3">
         <v>0.36349999999999999</v>
       </c>
-      <c r="F9" s="9">
-        <f t="shared" ref="F9:Q11" si="1">F$4*$E9</f>
+      <c r="F9" s="8">
+        <f t="shared" ref="F9:F11" si="2">F$4*$E9</f>
         <v>13916.234</v>
       </c>
-      <c r="G9" s="9">
-        <f t="shared" si="0"/>
+      <c r="G9" s="8">
+        <f t="shared" si="1"/>
         <v>13824.995499999999</v>
       </c>
-      <c r="H9" s="9">
-        <f t="shared" si="0"/>
+      <c r="H9" s="8">
+        <f t="shared" si="1"/>
         <v>13737.0285</v>
       </c>
-      <c r="I9" s="9">
-        <f t="shared" si="0"/>
+      <c r="I9" s="8">
+        <f t="shared" si="1"/>
         <v>12296.477999999999</v>
       </c>
-      <c r="J9" s="9">
-        <f t="shared" si="0"/>
+      <c r="J9" s="8">
+        <f t="shared" si="1"/>
         <v>11498.595499999999</v>
       </c>
-      <c r="K9" s="9">
-        <f t="shared" si="0"/>
+      <c r="K9" s="8">
+        <f t="shared" si="1"/>
         <v>11273.952499999999</v>
       </c>
-      <c r="L9" s="9">
-        <f t="shared" si="0"/>
+      <c r="L9" s="8">
+        <f t="shared" si="1"/>
         <v>11180.1695</v>
       </c>
-      <c r="M9" s="9">
-        <f t="shared" si="0"/>
+      <c r="M9" s="8">
+        <f t="shared" si="1"/>
         <v>11449.886500000001</v>
       </c>
-      <c r="N9" s="9">
-        <f t="shared" si="0"/>
+      <c r="N9" s="8">
+        <f t="shared" si="1"/>
         <v>12213.6</v>
       </c>
-      <c r="O9" s="9">
-        <f t="shared" si="0"/>
+      <c r="O9" s="8">
+        <f t="shared" si="1"/>
         <v>12472.7755</v>
       </c>
-      <c r="P9" s="9">
-        <f t="shared" si="0"/>
+      <c r="P9" s="8">
+        <f t="shared" si="1"/>
         <v>12400.075499999999</v>
       </c>
-      <c r="Q9" s="9">
-        <f t="shared" si="0"/>
+      <c r="Q9" s="8">
+        <f t="shared" si="1"/>
         <v>12850.451999999999</v>
       </c>
-    </row>
-    <row r="10" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="T9">
+        <v>4</v>
+      </c>
+      <c r="U9" t="s">
+        <v>18</v>
+      </c>
+      <c r="V9">
+        <v>2028</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="0"/>
+        <v>10.60392425279489</v>
+      </c>
+      <c r="X9">
+        <v>92954</v>
+      </c>
+    </row>
+    <row r="10" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D10" s="2">
         <v>3</v>
       </c>
       <c r="E10" s="3">
         <v>0.46920000000000001</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
+        <f t="shared" si="2"/>
+        <v>17962.852800000001</v>
+      </c>
+      <c r="G10" s="8">
         <f t="shared" si="1"/>
-        <v>17962.852800000001</v>
-      </c>
-      <c r="G10" s="9">
-        <f t="shared" si="0"/>
         <v>17845.083600000002</v>
       </c>
-      <c r="H10" s="9">
-        <f t="shared" si="0"/>
+      <c r="H10" s="8">
+        <f t="shared" si="1"/>
         <v>17731.537199999999</v>
       </c>
-      <c r="I10" s="9">
-        <f t="shared" si="0"/>
+      <c r="I10" s="8">
+        <f t="shared" si="1"/>
         <v>15872.097600000001</v>
       </c>
-      <c r="J10" s="9">
-        <f t="shared" si="0"/>
+      <c r="J10" s="8">
+        <f t="shared" si="1"/>
         <v>14842.203600000001</v>
       </c>
-      <c r="K10" s="9">
-        <f t="shared" si="0"/>
+      <c r="K10" s="8">
+        <f t="shared" si="1"/>
         <v>14552.237999999999</v>
       </c>
-      <c r="L10" s="9">
-        <f t="shared" si="0"/>
+      <c r="L10" s="8">
+        <f t="shared" si="1"/>
         <v>14431.1844</v>
       </c>
-      <c r="M10" s="9">
-        <f t="shared" si="0"/>
+      <c r="M10" s="8">
+        <f t="shared" si="1"/>
         <v>14779.3308</v>
       </c>
-      <c r="N10" s="9">
-        <f t="shared" si="0"/>
+      <c r="N10" s="8">
+        <f t="shared" si="1"/>
         <v>15765.12</v>
       </c>
-      <c r="O10" s="9">
-        <f t="shared" si="0"/>
+      <c r="O10" s="8">
+        <f t="shared" si="1"/>
         <v>16099.659600000001</v>
       </c>
-      <c r="P10" s="9">
-        <f t="shared" si="0"/>
+      <c r="P10" s="8">
+        <f t="shared" si="1"/>
         <v>16005.819600000001</v>
       </c>
-      <c r="Q10" s="9">
-        <f t="shared" si="0"/>
+      <c r="Q10" s="8">
+        <f t="shared" si="1"/>
         <v>16587.1584</v>
       </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="T10">
+        <v>5</v>
+      </c>
+      <c r="U10" t="s">
+        <v>18</v>
+      </c>
+      <c r="V10">
+        <v>2029</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="0"/>
+        <v>10.996577686516085</v>
+      </c>
+      <c r="X10">
+        <v>96396</v>
+      </c>
+    </row>
+    <row r="11" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D11" s="2">
         <v>4</v>
       </c>
       <c r="E11" s="3">
         <v>0.15359999999999999</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
+        <f t="shared" si="2"/>
+        <v>5880.4223999999995</v>
+      </c>
+      <c r="G11" s="8">
         <f t="shared" si="1"/>
-        <v>5880.4223999999995</v>
-      </c>
-      <c r="G11" s="9">
-        <f t="shared" si="0"/>
         <v>5841.8687999999993</v>
       </c>
-      <c r="H11" s="9">
-        <f t="shared" si="0"/>
+      <c r="H11" s="8">
+        <f t="shared" si="1"/>
         <v>5804.6975999999995</v>
       </c>
-      <c r="I11" s="9">
-        <f t="shared" si="0"/>
+      <c r="I11" s="8">
+        <f t="shared" si="1"/>
         <v>5195.9807999999994</v>
       </c>
-      <c r="J11" s="9">
-        <f t="shared" si="0"/>
+      <c r="J11" s="8">
+        <f t="shared" si="1"/>
         <v>4858.8287999999993</v>
       </c>
-      <c r="K11" s="9">
-        <f t="shared" si="0"/>
+      <c r="K11" s="8">
+        <f t="shared" si="1"/>
         <v>4763.9039999999995</v>
       </c>
-      <c r="L11" s="9">
-        <f t="shared" si="0"/>
+      <c r="L11" s="8">
+        <f t="shared" si="1"/>
         <v>4724.2752</v>
       </c>
-      <c r="M11" s="9">
-        <f t="shared" si="0"/>
+      <c r="M11" s="8">
+        <f t="shared" si="1"/>
         <v>4838.2464</v>
       </c>
-      <c r="N11" s="9">
-        <f t="shared" si="0"/>
+      <c r="N11" s="8">
+        <f t="shared" si="1"/>
         <v>5160.9599999999991</v>
       </c>
-      <c r="O11" s="9">
-        <f t="shared" si="0"/>
+      <c r="O11" s="8">
+        <f t="shared" si="1"/>
         <v>5270.4767999999995</v>
       </c>
-      <c r="P11" s="9">
-        <f t="shared" si="0"/>
+      <c r="P11" s="8">
+        <f t="shared" si="1"/>
         <v>5239.7567999999992</v>
       </c>
-      <c r="Q11" s="9">
-        <f t="shared" si="0"/>
+      <c r="Q11" s="8">
+        <f t="shared" si="1"/>
         <v>5430.0671999999995</v>
       </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="T11">
+        <v>6</v>
+      </c>
+      <c r="U11" t="s">
+        <v>18</v>
+      </c>
+      <c r="V11">
+        <v>2030</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="0"/>
+        <v>11.413757700205339</v>
+      </c>
+      <c r="X11">
+        <v>100053</v>
+      </c>
+    </row>
+    <row r="12" spans="4:25" x14ac:dyDescent="0.3">
+      <c r="T12">
+        <v>7</v>
+      </c>
+      <c r="U12" t="s">
+        <v>18</v>
+      </c>
+      <c r="V12">
+        <v>2031</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="0"/>
+        <v>11.723248916267396</v>
+      </c>
+      <c r="X12">
+        <v>102766</v>
+      </c>
+    </row>
+    <row r="13" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="T13">
+        <v>8</v>
+      </c>
+      <c r="U13" t="s">
+        <v>18</v>
+      </c>
+      <c r="V13">
+        <v>2032</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="0"/>
+        <v>12.043919689710243</v>
+      </c>
+      <c r="X13">
+        <v>105577</v>
+      </c>
+    </row>
+    <row r="14" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D14" s="4">
         <v>1</v>
       </c>
       <c r="E14" s="1">
         <v>45292</v>
       </c>
-    </row>
-    <row r="15" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="T14">
+        <v>9</v>
+      </c>
+      <c r="U14" t="s">
+        <v>18</v>
+      </c>
+      <c r="V14">
+        <v>2033</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="0"/>
+        <v>12.480949121606205</v>
+      </c>
+      <c r="X14">
+        <v>109408</v>
+      </c>
+    </row>
+    <row r="15" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D15" s="2">
         <v>1</v>
       </c>
       <c r="E15" s="5">
         <v>1.3753</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="8">
         <f>$E15*F8</f>
         <v>721.33219724000003</v>
       </c>
-      <c r="G15" s="9">
-        <f t="shared" ref="G15:Q15" si="2">$E15*G8</f>
+      <c r="G15" s="8">
+        <f t="shared" ref="G15:Q15" si="3">$E15*G8</f>
         <v>716.60295312999995</v>
       </c>
-      <c r="H15" s="9">
-        <f t="shared" si="2"/>
+      <c r="H15" s="8">
+        <f t="shared" si="3"/>
         <v>712.04328351000004</v>
       </c>
-      <c r="I15" s="9">
-        <f t="shared" si="2"/>
+      <c r="I15" s="8">
+        <f t="shared" si="3"/>
         <v>637.37398308000002</v>
       </c>
-      <c r="J15" s="9">
-        <f t="shared" si="2"/>
+      <c r="J15" s="8">
+        <f t="shared" si="3"/>
         <v>596.01664913000002</v>
       </c>
-      <c r="K15" s="9">
-        <f t="shared" si="2"/>
+      <c r="K15" s="8">
+        <f t="shared" si="3"/>
         <v>584.37253414999998</v>
       </c>
-      <c r="L15" s="9">
-        <f t="shared" si="2"/>
+      <c r="L15" s="8">
+        <f t="shared" si="3"/>
         <v>579.51139877000003</v>
       </c>
-      <c r="M15" s="9">
-        <f t="shared" si="2"/>
+      <c r="M15" s="8">
+        <f t="shared" si="3"/>
         <v>593.49187339000002</v>
       </c>
-      <c r="N15" s="9">
-        <f t="shared" si="2"/>
+      <c r="N15" s="8">
+        <f t="shared" si="3"/>
         <v>633.07809599999996</v>
       </c>
-      <c r="O15" s="9">
-        <f t="shared" si="2"/>
+      <c r="O15" s="8">
+        <f t="shared" si="3"/>
         <v>646.51216392999993</v>
       </c>
-      <c r="P15" s="9">
-        <f t="shared" si="2"/>
+      <c r="P15" s="8">
+        <f t="shared" si="3"/>
         <v>642.74384192999992</v>
       </c>
-      <c r="Q15" s="9">
-        <f t="shared" si="2"/>
+      <c r="Q15" s="8">
+        <f t="shared" si="3"/>
         <v>666.08859672000006</v>
       </c>
-    </row>
-    <row r="16" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="T15">
+        <v>10</v>
+      </c>
+      <c r="U15" t="s">
+        <v>18</v>
+      </c>
+      <c r="V15">
+        <v>2034</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="0"/>
+        <v>12.800365046771617</v>
+      </c>
+      <c r="X15">
+        <v>112208</v>
+      </c>
+    </row>
+    <row r="16" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D16" s="2">
         <v>2</v>
       </c>
       <c r="E16" s="5">
         <v>1.1469</v>
       </c>
-      <c r="F16" s="9">
-        <f t="shared" ref="F16:Q16" si="3">$E16*F9</f>
+      <c r="F16" s="8">
+        <f t="shared" ref="F16:Q16" si="4">$E16*F9</f>
         <v>15960.528774600001</v>
       </c>
-      <c r="G16" s="9">
-        <f t="shared" si="3"/>
+      <c r="G16" s="8">
+        <f t="shared" si="4"/>
         <v>15855.887338949999</v>
       </c>
-      <c r="H16" s="9">
-        <f t="shared" si="3"/>
+      <c r="H16" s="8">
+        <f t="shared" si="4"/>
         <v>15754.997986650002</v>
       </c>
-      <c r="I16" s="9">
-        <f t="shared" si="3"/>
+      <c r="I16" s="8">
+        <f t="shared" si="4"/>
         <v>14102.8306182</v>
       </c>
-      <c r="J16" s="9">
-        <f t="shared" si="3"/>
+      <c r="J16" s="8">
+        <f t="shared" si="4"/>
         <v>13187.73917895</v>
       </c>
-      <c r="K16" s="9">
-        <f t="shared" si="3"/>
+      <c r="K16" s="8">
+        <f t="shared" si="4"/>
         <v>12930.096122249999</v>
       </c>
-      <c r="L16" s="9">
-        <f t="shared" si="3"/>
+      <c r="L16" s="8">
+        <f t="shared" si="4"/>
         <v>12822.536399550001</v>
       </c>
-      <c r="M16" s="9">
-        <f t="shared" si="3"/>
+      <c r="M16" s="8">
+        <f t="shared" si="4"/>
         <v>13131.87482685</v>
       </c>
-      <c r="N16" s="9">
-        <f t="shared" si="3"/>
+      <c r="N16" s="8">
+        <f t="shared" si="4"/>
         <v>14007.777840000001</v>
       </c>
-      <c r="O16" s="9">
-        <f t="shared" si="3"/>
+      <c r="O16" s="8">
+        <f t="shared" si="4"/>
         <v>14305.02622095</v>
       </c>
-      <c r="P16" s="9">
-        <f t="shared" si="3"/>
+      <c r="P16" s="8">
+        <f t="shared" si="4"/>
         <v>14221.646590949998</v>
       </c>
-      <c r="Q16" s="9">
-        <f t="shared" si="3"/>
+      <c r="Q16" s="8">
+        <f t="shared" si="4"/>
         <v>14738.1833988</v>
       </c>
-    </row>
-    <row r="17" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="T16">
+        <v>11</v>
+      </c>
+      <c r="U16" t="s">
+        <v>18</v>
+      </c>
+      <c r="V16">
+        <v>2035</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="0"/>
+        <v>13.139858544375999</v>
+      </c>
+      <c r="X16">
+        <v>115184</v>
+      </c>
+    </row>
+    <row r="17" spans="4:24" x14ac:dyDescent="0.3">
       <c r="D17" s="2">
         <v>3</v>
       </c>
       <c r="E17" s="5">
         <v>0.96589999999999998</v>
       </c>
-      <c r="F17" s="9">
-        <f t="shared" ref="F17:Q17" si="4">$E17*F10</f>
+      <c r="F17" s="8">
+        <f t="shared" ref="F17:Q17" si="5">$E17*F10</f>
         <v>17350.319519519999</v>
       </c>
-      <c r="G17" s="9">
-        <f t="shared" si="4"/>
+      <c r="G17" s="8">
+        <f t="shared" si="5"/>
         <v>17236.566249240001</v>
       </c>
-      <c r="H17" s="9">
-        <f t="shared" si="4"/>
+      <c r="H17" s="8">
+        <f t="shared" si="5"/>
         <v>17126.891781479997</v>
       </c>
-      <c r="I17" s="9">
-        <f t="shared" si="4"/>
+      <c r="I17" s="8">
+        <f t="shared" si="5"/>
         <v>15330.859071840001</v>
       </c>
-      <c r="J17" s="9">
-        <f t="shared" si="4"/>
+      <c r="J17" s="8">
+        <f t="shared" si="5"/>
         <v>14336.08445724</v>
       </c>
-      <c r="K17" s="9">
-        <f t="shared" si="4"/>
+      <c r="K17" s="8">
+        <f t="shared" si="5"/>
         <v>14056.0066842</v>
       </c>
-      <c r="L17" s="9">
-        <f t="shared" si="4"/>
+      <c r="L17" s="8">
+        <f t="shared" si="5"/>
         <v>13939.081011959999</v>
       </c>
-      <c r="M17" s="9">
-        <f t="shared" si="4"/>
+      <c r="M17" s="8">
+        <f t="shared" si="5"/>
         <v>14275.35561972</v>
       </c>
-      <c r="N17" s="9">
-        <f t="shared" si="4"/>
+      <c r="N17" s="8">
+        <f t="shared" si="5"/>
         <v>15227.529408</v>
       </c>
-      <c r="O17" s="9">
-        <f t="shared" si="4"/>
+      <c r="O17" s="8">
+        <f t="shared" si="5"/>
         <v>15550.66120764</v>
       </c>
-      <c r="P17" s="9">
-        <f t="shared" si="4"/>
+      <c r="P17" s="8">
+        <f t="shared" si="5"/>
         <v>15460.02115164</v>
       </c>
-      <c r="Q17" s="9">
-        <f t="shared" si="4"/>
+      <c r="Q17" s="8">
+        <f t="shared" si="5"/>
         <v>16021.53629856</v>
       </c>
-    </row>
-    <row r="18" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="T17">
+        <v>12</v>
+      </c>
+      <c r="U17" t="s">
+        <v>18</v>
+      </c>
+      <c r="V17">
+        <v>2036</v>
+      </c>
+      <c r="W17">
+        <f t="shared" si="0"/>
+        <v>13.509468400638832</v>
+      </c>
+      <c r="X17">
+        <v>118424</v>
+      </c>
+    </row>
+    <row r="18" spans="4:24" x14ac:dyDescent="0.3">
       <c r="D18" s="2">
         <v>4</v>
       </c>
       <c r="E18" s="5">
         <v>0.72309999999999997</v>
       </c>
-      <c r="F18" s="9">
-        <f t="shared" ref="F18:Q18" si="5">$E18*F11</f>
+      <c r="F18" s="8">
+        <f t="shared" ref="F18:Q18" si="6">$E18*F11</f>
         <v>4252.1334374399994</v>
       </c>
-      <c r="G18" s="9">
-        <f t="shared" si="5"/>
+      <c r="G18" s="8">
+        <f t="shared" si="6"/>
         <v>4224.2553292799994</v>
       </c>
-      <c r="H18" s="9">
-        <f t="shared" si="5"/>
+      <c r="H18" s="8">
+        <f t="shared" si="6"/>
         <v>4197.3768345599992</v>
       </c>
-      <c r="I18" s="9">
-        <f t="shared" si="5"/>
+      <c r="I18" s="8">
+        <f t="shared" si="6"/>
         <v>3757.2137164799992</v>
       </c>
-      <c r="J18" s="9">
-        <f t="shared" si="5"/>
+      <c r="J18" s="8">
+        <f t="shared" si="6"/>
         <v>3513.4191052799993</v>
       </c>
-      <c r="K18" s="9">
-        <f t="shared" si="5"/>
+      <c r="K18" s="8">
+        <f t="shared" si="6"/>
         <v>3444.7789823999997</v>
       </c>
-      <c r="L18" s="9">
-        <f t="shared" si="5"/>
+      <c r="L18" s="8">
+        <f t="shared" si="6"/>
         <v>3416.1233971199999</v>
       </c>
-      <c r="M18" s="9">
-        <f t="shared" si="5"/>
+      <c r="M18" s="8">
+        <f t="shared" si="6"/>
         <v>3498.53597184</v>
       </c>
-      <c r="N18" s="9">
-        <f t="shared" si="5"/>
+      <c r="N18" s="8">
+        <f t="shared" si="6"/>
         <v>3731.890175999999</v>
       </c>
-      <c r="O18" s="9">
-        <f t="shared" si="5"/>
+      <c r="O18" s="8">
+        <f t="shared" si="6"/>
         <v>3811.0817740799994</v>
       </c>
-      <c r="P18" s="9">
-        <f t="shared" si="5"/>
+      <c r="P18" s="8">
+        <f t="shared" si="6"/>
         <v>3788.8681420799994</v>
       </c>
-      <c r="Q18" s="9">
-        <f t="shared" si="5"/>
+      <c r="Q18" s="8">
+        <f t="shared" si="6"/>
         <v>3926.4815923199994</v>
+      </c>
+      <c r="T18">
+        <v>13</v>
+      </c>
+      <c r="U18" t="s">
+        <v>18</v>
+      </c>
+      <c r="V18">
+        <v>2037</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="0"/>
+        <v>13.889915582934064</v>
+      </c>
+      <c r="X18">
+        <v>121759</v>
+      </c>
+    </row>
+    <row r="19" spans="4:24" x14ac:dyDescent="0.3">
+      <c r="T19">
+        <v>14</v>
+      </c>
+      <c r="U19" t="s">
+        <v>18</v>
+      </c>
+      <c r="V19">
+        <v>2038</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="0"/>
+        <v>14.272644307551905</v>
+      </c>
+      <c r="X19">
+        <v>125114</v>
+      </c>
+    </row>
+    <row r="20" spans="4:24" x14ac:dyDescent="0.3">
+      <c r="T20">
+        <v>15</v>
+      </c>
+      <c r="U20" t="s">
+        <v>19</v>
+      </c>
+      <c r="V20">
+        <v>2024</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="0"/>
+        <v>21.982432124115903</v>
+      </c>
+      <c r="X20">
+        <v>192698</v>
+      </c>
+    </row>
+    <row r="21" spans="4:24" x14ac:dyDescent="0.3">
+      <c r="T21">
+        <v>16</v>
+      </c>
+      <c r="U21" t="s">
+        <v>19</v>
+      </c>
+      <c r="V21">
+        <v>2025</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="0"/>
+        <v>21.727469769564227</v>
+      </c>
+      <c r="X21">
+        <v>190463</v>
+      </c>
+    </row>
+    <row r="22" spans="4:24" x14ac:dyDescent="0.3">
+      <c r="T22">
+        <v>17</v>
+      </c>
+      <c r="U22" t="s">
+        <v>19</v>
+      </c>
+      <c r="V22">
+        <v>2026</v>
+      </c>
+      <c r="W22">
+        <f t="shared" si="0"/>
+        <v>21.70784850558978</v>
+      </c>
+      <c r="X22">
+        <v>190291</v>
+      </c>
+    </row>
+    <row r="23" spans="4:24" x14ac:dyDescent="0.3">
+      <c r="T23">
+        <v>18</v>
+      </c>
+      <c r="U23" t="s">
+        <v>19</v>
+      </c>
+      <c r="V23">
+        <v>2027</v>
+      </c>
+      <c r="W23">
+        <f t="shared" si="0"/>
+        <v>21.870978781656401</v>
+      </c>
+      <c r="X23">
+        <v>191721</v>
+      </c>
+    </row>
+    <row r="24" spans="4:24" x14ac:dyDescent="0.3">
+      <c r="T24">
+        <v>19</v>
+      </c>
+      <c r="U24" t="s">
+        <v>19</v>
+      </c>
+      <c r="V24">
+        <v>2028</v>
+      </c>
+      <c r="W24">
+        <f t="shared" si="0"/>
+        <v>22.066735112936346</v>
+      </c>
+      <c r="X24">
+        <v>193437</v>
+      </c>
+    </row>
+    <row r="25" spans="4:24" x14ac:dyDescent="0.3">
+      <c r="T25">
+        <v>20</v>
+      </c>
+      <c r="U25" t="s">
+        <v>19</v>
+      </c>
+      <c r="V25">
+        <v>2029</v>
+      </c>
+      <c r="W25">
+        <f t="shared" si="0"/>
+        <v>22.434747889573352</v>
+      </c>
+      <c r="X25">
+        <v>196663</v>
+      </c>
+    </row>
+    <row r="26" spans="4:24" x14ac:dyDescent="0.3">
+      <c r="T26">
+        <v>21</v>
+      </c>
+      <c r="U26" t="s">
+        <v>19</v>
+      </c>
+      <c r="V26">
+        <v>2030</v>
+      </c>
+      <c r="W26">
+        <f t="shared" si="0"/>
+        <v>22.684804928131417</v>
+      </c>
+      <c r="X26">
+        <v>198855</v>
+      </c>
+    </row>
+    <row r="27" spans="4:24" x14ac:dyDescent="0.3">
+      <c r="T27">
+        <v>22</v>
+      </c>
+      <c r="U27" t="s">
+        <v>19</v>
+      </c>
+      <c r="V27">
+        <v>2031</v>
+      </c>
+      <c r="W27">
+        <f t="shared" si="0"/>
+        <v>22.995665069587041</v>
+      </c>
+      <c r="X27">
+        <v>201580</v>
+      </c>
+    </row>
+    <row r="28" spans="4:24" x14ac:dyDescent="0.3">
+      <c r="T28">
+        <v>23</v>
+      </c>
+      <c r="U28" t="s">
+        <v>19</v>
+      </c>
+      <c r="V28">
+        <v>2032</v>
+      </c>
+      <c r="W28">
+        <f t="shared" si="0"/>
+        <v>23.33504449007529</v>
+      </c>
+      <c r="X28">
+        <v>204555</v>
+      </c>
+    </row>
+    <row r="29" spans="4:24" x14ac:dyDescent="0.3">
+      <c r="T29">
+        <v>24</v>
+      </c>
+      <c r="U29" t="s">
+        <v>19</v>
+      </c>
+      <c r="V29">
+        <v>2033</v>
+      </c>
+      <c r="W29">
+        <f t="shared" si="0"/>
+        <v>23.700205338809035</v>
+      </c>
+      <c r="X29">
+        <v>207756</v>
+      </c>
+    </row>
+    <row r="30" spans="4:24" x14ac:dyDescent="0.3">
+      <c r="T30">
+        <v>25</v>
+      </c>
+      <c r="U30" t="s">
+        <v>19</v>
+      </c>
+      <c r="V30">
+        <v>2034</v>
+      </c>
+      <c r="W30">
+        <f t="shared" si="0"/>
+        <v>24.103353867214238</v>
+      </c>
+      <c r="X30">
+        <v>211290</v>
+      </c>
+    </row>
+    <row r="31" spans="4:24" x14ac:dyDescent="0.3">
+      <c r="T31">
+        <v>26</v>
+      </c>
+      <c r="U31" t="s">
+        <v>19</v>
+      </c>
+      <c r="V31">
+        <v>2035</v>
+      </c>
+      <c r="W31">
+        <f t="shared" si="0"/>
+        <v>24.528519279032626</v>
+      </c>
+      <c r="X31">
+        <v>215017</v>
+      </c>
+    </row>
+    <row r="32" spans="4:24" x14ac:dyDescent="0.3">
+      <c r="T32">
+        <v>27</v>
+      </c>
+      <c r="U32" t="s">
+        <v>19</v>
+      </c>
+      <c r="V32">
+        <v>2036</v>
+      </c>
+      <c r="W32">
+        <f t="shared" si="0"/>
+        <v>25.014145562400184</v>
+      </c>
+      <c r="X32">
+        <v>219274</v>
+      </c>
+    </row>
+    <row r="33" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T33">
+        <v>28</v>
+      </c>
+      <c r="U33" t="s">
+        <v>19</v>
+      </c>
+      <c r="V33">
+        <v>2037</v>
+      </c>
+      <c r="W33">
+        <f t="shared" si="0"/>
+        <v>25.555555555555557</v>
+      </c>
+      <c r="X33">
+        <v>224020</v>
+      </c>
+    </row>
+    <row r="34" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T34">
+        <v>29</v>
+      </c>
+      <c r="U34" t="s">
+        <v>19</v>
+      </c>
+      <c r="V34">
+        <v>2038</v>
+      </c>
+      <c r="W34">
+        <f t="shared" si="0"/>
+        <v>26.134953228382386</v>
+      </c>
+      <c r="X34">
+        <v>229099</v>
+      </c>
+    </row>
+    <row r="35" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T35">
+        <v>30</v>
+      </c>
+      <c r="U35" t="s">
+        <v>20</v>
+      </c>
+      <c r="V35">
+        <v>2024</v>
+      </c>
+      <c r="W35">
+        <f t="shared" si="0"/>
+        <v>13.879534565366187</v>
+      </c>
+      <c r="X35">
+        <v>121668</v>
+      </c>
+    </row>
+    <row r="36" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T36">
+        <v>31</v>
+      </c>
+      <c r="U36" t="s">
+        <v>20</v>
+      </c>
+      <c r="V36">
+        <v>2025</v>
+      </c>
+      <c r="W36">
+        <f t="shared" si="0"/>
+        <v>14.189025781428246</v>
+      </c>
+      <c r="X36">
+        <v>124381</v>
+      </c>
+    </row>
+    <row r="37" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T37">
+        <v>32</v>
+      </c>
+      <c r="U37" t="s">
+        <v>20</v>
+      </c>
+      <c r="V37">
+        <v>2026</v>
+      </c>
+      <c r="W37">
+        <f t="shared" si="0"/>
+        <v>14.669404517453799</v>
+      </c>
+      <c r="X37">
+        <v>128592</v>
+      </c>
+    </row>
+    <row r="38" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T38">
+        <v>33</v>
+      </c>
+      <c r="U38" t="s">
+        <v>20</v>
+      </c>
+      <c r="V38">
+        <v>2027</v>
+      </c>
+      <c r="W38">
+        <f t="shared" si="0"/>
+        <v>15.204996577686517</v>
+      </c>
+      <c r="X38">
+        <v>133287</v>
+      </c>
+    </row>
+    <row r="39" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T39">
+        <v>34</v>
+      </c>
+      <c r="U39" t="s">
+        <v>20</v>
+      </c>
+      <c r="V39">
+        <v>2028</v>
+      </c>
+      <c r="W39">
+        <f t="shared" si="0"/>
+        <v>15.82569016655259</v>
+      </c>
+      <c r="X39">
+        <v>138728</v>
+      </c>
+    </row>
+    <row r="40" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T40">
+        <v>35</v>
+      </c>
+      <c r="U40" t="s">
+        <v>20</v>
+      </c>
+      <c r="V40">
+        <v>2029</v>
+      </c>
+      <c r="W40">
+        <f t="shared" si="0"/>
+        <v>16.472735569244808</v>
+      </c>
+      <c r="X40">
+        <v>144400</v>
+      </c>
+    </row>
+    <row r="41" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T41">
+        <v>36</v>
+      </c>
+      <c r="U41" t="s">
+        <v>20</v>
+      </c>
+      <c r="V41">
+        <v>2030</v>
+      </c>
+      <c r="W41">
+        <f t="shared" si="0"/>
+        <v>17.125941136208077</v>
+      </c>
+      <c r="X41">
+        <v>150126</v>
+      </c>
+    </row>
+    <row r="42" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T42">
+        <v>37</v>
+      </c>
+      <c r="U42" t="s">
+        <v>20</v>
+      </c>
+      <c r="V42">
+        <v>2031</v>
+      </c>
+      <c r="W42">
+        <f t="shared" si="0"/>
+        <v>17.822381930184804</v>
+      </c>
+      <c r="X42">
+        <v>156231</v>
+      </c>
+    </row>
+    <row r="43" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T43">
+        <v>38</v>
+      </c>
+      <c r="U43" t="s">
+        <v>20</v>
+      </c>
+      <c r="V43">
+        <v>2032</v>
+      </c>
+      <c r="W43">
+        <f t="shared" si="0"/>
+        <v>18.533082363677845</v>
+      </c>
+      <c r="X43">
+        <v>162461</v>
+      </c>
+    </row>
+    <row r="44" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T44">
+        <v>39</v>
+      </c>
+      <c r="U44" t="s">
+        <v>20</v>
+      </c>
+      <c r="V44">
+        <v>2033</v>
+      </c>
+      <c r="W44">
+        <f t="shared" si="0"/>
+        <v>19.300365046771617</v>
+      </c>
+      <c r="X44">
+        <v>169187</v>
+      </c>
+    </row>
+    <row r="45" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T45">
+        <v>40</v>
+      </c>
+      <c r="U45" t="s">
+        <v>20</v>
+      </c>
+      <c r="V45">
+        <v>2034</v>
+      </c>
+      <c r="W45">
+        <f t="shared" si="0"/>
+        <v>20.083390371891397</v>
+      </c>
+      <c r="X45">
+        <v>176051</v>
+      </c>
+    </row>
+    <row r="46" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T46">
+        <v>41</v>
+      </c>
+      <c r="U46" t="s">
+        <v>20</v>
+      </c>
+      <c r="V46">
+        <v>2035</v>
+      </c>
+      <c r="W46">
+        <f t="shared" si="0"/>
+        <v>20.854209445585216</v>
+      </c>
+      <c r="X46">
+        <v>182808</v>
+      </c>
+    </row>
+    <row r="47" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T47">
+        <v>42</v>
+      </c>
+      <c r="U47" t="s">
+        <v>20</v>
+      </c>
+      <c r="V47">
+        <v>2036</v>
+      </c>
+      <c r="W47">
+        <f t="shared" si="0"/>
+        <v>21.688797627195985</v>
+      </c>
+      <c r="X47">
+        <v>190124</v>
+      </c>
+    </row>
+    <row r="48" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T48">
+        <v>43</v>
+      </c>
+      <c r="U48" t="s">
+        <v>20</v>
+      </c>
+      <c r="V48">
+        <v>2037</v>
+      </c>
+      <c r="W48">
+        <f t="shared" si="0"/>
+        <v>22.546315309148984</v>
+      </c>
+      <c r="X48">
+        <v>197641</v>
+      </c>
+    </row>
+    <row r="49" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T49">
+        <v>44</v>
+      </c>
+      <c r="U49" t="s">
+        <v>20</v>
+      </c>
+      <c r="V49">
+        <v>2038</v>
+      </c>
+      <c r="W49">
+        <f t="shared" si="0"/>
+        <v>23.364704540269223</v>
+      </c>
+      <c r="X49">
+        <v>204815</v>
+      </c>
+    </row>
+    <row r="50" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T50">
+        <v>45</v>
+      </c>
+      <c r="U50" t="s">
+        <v>17</v>
+      </c>
+      <c r="V50">
+        <v>2024</v>
+      </c>
+      <c r="W50">
+        <f t="shared" si="0"/>
+        <v>50.312571298197582</v>
+      </c>
+      <c r="X50">
+        <v>441040</v>
+      </c>
+    </row>
+    <row r="51" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T51">
+        <v>46</v>
+      </c>
+      <c r="U51" t="s">
+        <v>17</v>
+      </c>
+      <c r="V51">
+        <v>2025</v>
+      </c>
+      <c r="W51">
+        <f t="shared" si="0"/>
+        <v>50.925507643166782</v>
+      </c>
+      <c r="X51">
+        <v>446413</v>
+      </c>
+    </row>
+    <row r="52" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T52">
+        <v>47</v>
+      </c>
+      <c r="U52" t="s">
+        <v>17</v>
+      </c>
+      <c r="V52">
+        <v>2026</v>
+      </c>
+      <c r="W52">
+        <f t="shared" si="0"/>
+        <v>52.42961441934748</v>
+      </c>
+      <c r="X52">
+        <v>459598</v>
+      </c>
+    </row>
+    <row r="53" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T53">
+        <v>48</v>
+      </c>
+      <c r="U53" t="s">
+        <v>17</v>
+      </c>
+      <c r="V53">
+        <v>2027</v>
+      </c>
+      <c r="W53">
+        <f t="shared" si="0"/>
+        <v>54.183093771389458</v>
+      </c>
+      <c r="X53">
+        <v>474969</v>
+      </c>
+    </row>
+    <row r="54" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T54">
+        <v>49</v>
+      </c>
+      <c r="U54" t="s">
+        <v>17</v>
+      </c>
+      <c r="V54">
+        <v>2028</v>
+      </c>
+      <c r="W54">
+        <f t="shared" si="0"/>
+        <v>56.141341546885698</v>
+      </c>
+      <c r="X54">
+        <v>492135</v>
+      </c>
+    </row>
+    <row r="55" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T55">
+        <v>50</v>
+      </c>
+      <c r="U55" t="s">
+        <v>17</v>
+      </c>
+      <c r="V55">
+        <v>2029</v>
+      </c>
+      <c r="W55">
+        <f t="shared" si="0"/>
+        <v>58.090691307323752</v>
+      </c>
+      <c r="X55">
+        <v>509223</v>
+      </c>
+    </row>
+    <row r="56" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T56">
+        <v>51</v>
+      </c>
+      <c r="U56" t="s">
+        <v>17</v>
+      </c>
+      <c r="V56">
+        <v>2030</v>
+      </c>
+      <c r="W56">
+        <f t="shared" si="0"/>
+        <v>60.084074834588179</v>
+      </c>
+      <c r="X56">
+        <v>526697</v>
+      </c>
+    </row>
+    <row r="57" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T57">
+        <v>52</v>
+      </c>
+      <c r="U57" t="s">
+        <v>17</v>
+      </c>
+      <c r="V57">
+        <v>2031</v>
+      </c>
+      <c r="W57">
+        <f t="shared" si="0"/>
+        <v>62.253479352041978</v>
+      </c>
+      <c r="X57">
+        <v>545714</v>
+      </c>
+    </row>
+    <row r="58" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T58">
+        <v>53</v>
+      </c>
+      <c r="U58" t="s">
+        <v>17</v>
+      </c>
+      <c r="V58">
+        <v>2032</v>
+      </c>
+      <c r="W58">
+        <f t="shared" si="0"/>
+        <v>64.476386036960989</v>
+      </c>
+      <c r="X58">
+        <v>565200</v>
+      </c>
+    </row>
+    <row r="59" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T59">
+        <v>54</v>
+      </c>
+      <c r="U59" t="s">
+        <v>17</v>
+      </c>
+      <c r="V59">
+        <v>2033</v>
+      </c>
+      <c r="W59">
+        <f t="shared" si="0"/>
+        <v>66.846566278804474</v>
+      </c>
+      <c r="X59">
+        <v>585977</v>
+      </c>
+    </row>
+    <row r="60" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T60">
+        <v>55</v>
+      </c>
+      <c r="U60" t="s">
+        <v>17</v>
+      </c>
+      <c r="V60">
+        <v>2034</v>
+      </c>
+      <c r="W60">
+        <f t="shared" si="0"/>
+        <v>69.293406342687661</v>
+      </c>
+      <c r="X60">
+        <v>607426</v>
+      </c>
+    </row>
+    <row r="61" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T61">
+        <v>56</v>
+      </c>
+      <c r="U61" t="s">
+        <v>17</v>
+      </c>
+      <c r="V61">
+        <v>2035</v>
+      </c>
+      <c r="W61">
+        <f t="shared" si="0"/>
+        <v>71.818503308236373</v>
+      </c>
+      <c r="X61">
+        <v>629561</v>
+      </c>
+    </row>
+    <row r="62" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T62">
+        <v>57</v>
+      </c>
+      <c r="U62" t="s">
+        <v>17</v>
+      </c>
+      <c r="V62">
+        <v>2036</v>
+      </c>
+      <c r="W62">
+        <f t="shared" si="0"/>
+        <v>74.431895961670094</v>
+      </c>
+      <c r="X62">
+        <v>652470</v>
+      </c>
+    </row>
+    <row r="63" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T63">
+        <v>58</v>
+      </c>
+      <c r="U63" t="s">
+        <v>17</v>
+      </c>
+      <c r="V63">
+        <v>2037</v>
+      </c>
+      <c r="W63">
+        <f t="shared" si="0"/>
+        <v>77.11419119324664</v>
+      </c>
+      <c r="X63">
+        <v>675983</v>
+      </c>
+    </row>
+    <row r="64" spans="20:24" x14ac:dyDescent="0.3">
+      <c r="T64">
+        <v>59</v>
+      </c>
+      <c r="U64" t="s">
+        <v>17</v>
+      </c>
+      <c r="V64">
+        <v>2038</v>
+      </c>
+      <c r="W64">
+        <f t="shared" si="0"/>
+        <v>79.805612594113626</v>
+      </c>
+      <c r="X64">
+        <v>699576</v>
       </c>
     </row>
   </sheetData>
